--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE8E03F7-4FBD-495E-92BD-7DCE410BAAB3}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C4C47A-7846-4D5B-9B0B-09EFC23E3A8E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="272">
   <si>
     <t>Variable name</t>
   </si>
@@ -750,18 +750,6 @@
   </si>
   <si>
     <t>ZSFD</t>
-  </si>
-  <si>
-    <t>Slratio</t>
-  </si>
-  <si>
-    <t>Costs (small large ratio)</t>
-  </si>
-  <si>
-    <t>ZSLR</t>
-  </si>
-  <si>
-    <t>FTT-Fr small large ratio</t>
   </si>
   <si>
     <t>ZJET</t>
@@ -1233,10 +1221,10 @@
         <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1265,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1294,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1352,7 +1340,7 @@
         <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1381,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1410,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1439,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1453,7 +1441,7 @@
         <v>31090000</v>
       </c>
       <c r="D9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
@@ -1468,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1497,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1526,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1555,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1584,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1613,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1642,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1671,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1700,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1729,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -1776,10 +1764,10 @@
         <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1805,10 +1793,10 @@
         <v>54</v>
       </c>
       <c r="H2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1837,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1866,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1924,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1953,12 +1941,12 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1967,7 +1955,7 @@
         <v>-99</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
@@ -1982,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2011,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2040,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2069,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2098,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2127,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2156,7 +2144,7 @@
         <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2185,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2214,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2243,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2272,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2301,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -2330,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2359,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -2388,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -2417,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2457,10 +2445,10 @@
         <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2489,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2518,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2547,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2576,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2605,7 +2593,7 @@
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2634,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2663,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2692,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2721,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2750,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2779,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2808,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2837,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2866,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2895,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2921,10 +2909,10 @@
         <v>54</v>
       </c>
       <c r="H17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2965,10 +2953,10 @@
         <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2997,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -3026,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3055,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3084,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -3113,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -3142,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -3171,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -3200,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -3229,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -3258,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -3287,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -3316,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -3345,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -3374,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -3403,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3432,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -3461,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -3490,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -3519,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -3548,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -3577,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -3606,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -3635,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3664,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3674,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BB7FF7-82D6-482E-815B-F3751454FF7D}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3714,10 +3702,10 @@
         <v>187</v>
       </c>
       <c r="J1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -3734,7 +3722,7 @@
         <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -3752,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3787,12 +3775,12 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3822,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -3857,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3892,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -3927,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -3962,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -3997,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -4032,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -4067,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -4102,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -4137,164 +4125,164 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>35380000</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
         <v>238</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>35370000</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="I14" t="s">
         <v>239</v>
       </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I14" t="s">
-        <v>237</v>
-      </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>35380000</v>
+        <v>35230000</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
         <v>242</v>
       </c>
-      <c r="I15" t="s">
-        <v>243</v>
-      </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>35230000</v>
+        <v>35390000</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
         <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+        <v>246</v>
+      </c>
+      <c r="G16" t="s">
+        <v>54</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="I16" t="s">
-        <v>246</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
+        <v>245</v>
+      </c>
+      <c r="J16" t="s">
+        <v>257</v>
       </c>
       <c r="K16" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>35390000</v>
+        <v>35410000</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
-      </c>
-      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
         <v>250</v>
       </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" t="s">
-        <v>248</v>
-      </c>
       <c r="I17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J17" t="s">
-        <v>261</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>35410000</v>
+        <v>35420000</v>
       </c>
       <c r="D18" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -4302,46 +4290,11 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18" t="s">
-        <v>254</v>
-      </c>
-      <c r="I18" t="s">
-        <v>255</v>
-      </c>
       <c r="J18" t="s">
         <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>270</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>35420000</v>
-      </c>
-      <c r="D19" t="s">
-        <v>271</v>
-      </c>
-      <c r="E19" t="s">
-        <v>190</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4428,7 +4381,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
         <v>94</v>
@@ -4719,7 +4672,7 @@
         <v>185</v>
       </c>
       <c r="B46" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4743,15 +4696,15 @@
         <v>192</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4759,7 +4712,7 @@
         <v>212</v>
       </c>
       <c r="B51" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4767,7 +4720,7 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4775,7 +4728,7 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4783,7 +4736,7 @@
         <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4791,7 +4744,7 @@
         <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4799,7 +4752,7 @@
         <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4828,7 +4781,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B60" t="s">
         <v>93</v>
@@ -4839,39 +4792,39 @@
         <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B65" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4879,15 +4832,15 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B67" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FTT_StandAlone\Inputs\_MasterFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C4C47A-7846-4D5B-9B0B-09EFC23E3A8E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E6CE53-B410-4DDA-B35B-F2962674C9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="276">
   <si>
     <t>Variable name</t>
   </si>
@@ -858,6 +858,18 @@
   </si>
   <si>
     <t>FTT-Tr relative registration tax or subsidy</t>
+  </si>
+  <si>
+    <t>FTT-Fr City mapping</t>
+  </si>
+  <si>
+    <t>city mapping</t>
+  </si>
+  <si>
+    <t>region spillover</t>
+  </si>
+  <si>
+    <t>FTT-Fr Regional spillover matrix</t>
   </si>
 </sst>
 </file>
@@ -3662,12 +3674,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BB7FF7-82D6-482E-815B-F3751454FF7D}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
@@ -4297,14 +4309,73 @@
         <v>260</v>
       </c>
     </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>35430000</v>
+      </c>
+      <c r="D19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>35440000</v>
+      </c>
+      <c r="D20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA629D80-511C-42AD-ACB3-22237E3BD282}">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4840,6 +4911,14 @@
         <v>266</v>
       </c>
       <c r="B67" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>273</v>
+      </c>
+      <c r="B68" t="s">
         <v>248</v>
       </c>
     </row>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B21FCB0C-8A9E-F54D-8028-8000D713EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C900ADFB-7DD5-4FDD-9006-F74785241C29}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{B21FCB0C-8A9E-F54D-8028-8000D713EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFDFFA21-DC3F-4B1B-B7A8-2F7329923C4E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="520">
   <si>
     <t>Variable name</t>
   </si>
@@ -1607,16 +1607,13 @@
   </si>
   <si>
     <t>HMAN</t>
-  </si>
-  <si>
-    <t>FTT-Heat minimum sales mandate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1630,15 +1627,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1663,11 +1653,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1678,19 +1663,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4671,7 +4653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893746F0-70F0-4C21-8E46-9B5DBA6E54BB}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -5115,25 +5097,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>519</v>
+        <v>111</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="4">
-        <v>33190000</v>
+      <c r="C16">
+        <v>33110000</v>
       </c>
       <c r="D16" t="s">
-        <v>520</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
       </c>
-      <c r="G16">
-        <v>0</v>
+      <c r="G16" t="s">
+        <v>54</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5144,59 +5126,30 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>33110000</v>
+        <v>33010000</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
       </c>
-      <c r="H17">
-        <v>0</v>
+      <c r="H17" t="s">
+        <v>288</v>
       </c>
       <c r="I17" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>33010000</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" t="s">
-        <v>288</v>
-      </c>
-      <c r="I18" t="s">
         <v>291</v>
       </c>
     </row>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FTT_StandAlone\Inputs\_MasterFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E6CE53-B410-4DDA-B35B-F2962674C9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DF6274-83FA-405B-AF6B-8FAA23447639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4242,7 +4242,7 @@
         <v>257</v>
       </c>
       <c r="K16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FTT_StandAlone\Inputs\_MasterFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C4C47A-7846-4D5B-9B0B-09EFC23E3A8E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FF3758-B89F-41AC-AD73-A8A9FB5F181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -1189,16 +1189,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -1734,14 +1734,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04294AC-DBC1-4E51-84ED-2EC5066B9024}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>270</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2416,13 +2416,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893746F0-70F0-4C21-8E46-9B5DBA6E54BB}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>99</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>106</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>109</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>112</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>257</v>
       </c>
       <c r="I17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2923,14 +2923,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76D307B-9060-4C33-AF9D-2A846C2CA587}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.54296875" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>133</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>134</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>135</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>141</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>143</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>147</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>148</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>152</v>
       </c>
@@ -3663,17 +3663,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BB7FF7-82D6-482E-815B-F3751454FF7D}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>265</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>212</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>214</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>215</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>216</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>217</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>226</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>227</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>231</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>240</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>236</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>269</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>249</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -4305,9 +4305,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA629D80-511C-42AD-ACB3-22237E3BD282}">
   <dimension ref="A1:B67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>270</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>148</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>149</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>188</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>192</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>265</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>212</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>215</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>217</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>231</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>240</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>31</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>258</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>263</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>249</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>266</v>
       </c>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FTT_StandAlone\Inputs\_MasterFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FF3758-B89F-41AC-AD73-A8A9FB5F181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C4C47A-7846-4D5B-9B0B-09EFC23E3A8E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -1189,16 +1189,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -1734,14 +1734,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04294AC-DBC1-4E51-84ED-2EC5066B9024}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.7265625" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>270</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2416,13 +2416,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893746F0-70F0-4C21-8E46-9B5DBA6E54BB}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>99</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>109</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>112</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>257</v>
       </c>
       <c r="I17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2923,14 +2923,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76D307B-9060-4C33-AF9D-2A846C2CA587}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.54296875" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>133</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>134</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>135</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>141</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>143</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>147</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>148</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>152</v>
       </c>
@@ -3663,17 +3663,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BB7FF7-82D6-482E-815B-F3751454FF7D}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>265</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>212</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>214</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>215</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>216</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>217</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>226</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>227</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>231</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>240</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>236</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>269</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>249</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -4305,9 +4305,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA629D80-511C-42AD-ACB3-22237E3BD282}">
   <dimension ref="A1:B67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>270</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>148</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>149</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>188</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>192</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>265</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>212</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>215</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>217</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>231</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>240</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>31</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>258</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>263</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>249</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>266</v>
       </c>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uqcpaesd\Documents\GitHub\FTT_StandAlone\Inputs\_MasterFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2348AAE0-4093-464C-805C-FEA1C24F411E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73737E6C-1147-4030-A889-376A62E7AF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="285">
   <si>
     <t>Variable name</t>
   </si>
@@ -885,6 +885,18 @@
   </si>
   <si>
     <t>FTT-Price of electricity use (incl taxes)</t>
+  </si>
+  <si>
+    <t>FTT-Rooftop Solar PV Self-consumption rate</t>
+  </si>
+  <si>
+    <t>FTT-Rooftop Solar PV Feed-in-tariff</t>
+  </si>
+  <si>
+    <t>RSSC</t>
+  </si>
+  <si>
+    <t>RSFT</t>
   </si>
 </sst>
 </file>
@@ -1215,11 +1227,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="4" max="4" width="41.90625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="12.81640625" customWidth="1"/>
     <col min="7" max="7" width="14.453125" customWidth="1"/>
@@ -1802,6 +1814,64 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>33333333</v>
+      </c>
+      <c r="D21" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>33333334</v>
+      </c>
+      <c r="D22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
         <v>265</v>
       </c>
     </row>
@@ -4424,7 +4494,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA629D80-511C-42AD-ACB3-22237E3BD282}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -4976,6 +5046,22 @@
         <v>279</v>
       </c>
       <c r="B69" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>283</v>
+      </c>
+      <c r="B70" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B71" t="s">
         <v>278</v>
       </c>
     </row>

--- a/Inputs/_MasterFiles/FTT_variables.xlsx
+++ b/Inputs/_MasterFiles/FTT_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Inputs/_MasterFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FTT_StandAlone_GMP\Inputs\_MasterFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{96C6DCC7-F135-4F9F-BBD1-97530C10B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C4C47A-7846-4D5B-9B0B-09EFC23E3A8E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E2C91B-3A63-4CFF-9FB4-B7B702B1FFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTT-P" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="FTT-H" sheetId="3" r:id="rId3"/>
     <sheet name="FTT-S" sheetId="4" r:id="rId4"/>
     <sheet name="FTT-Fr" sheetId="7" r:id="rId5"/>
-    <sheet name="Time_Horizons" sheetId="6" r:id="rId6"/>
+    <sheet name="FTT-GMP" sheetId="8" r:id="rId6"/>
+    <sheet name="Time_Horizons" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FTT-P'!$A$1:$G$18</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="272">
   <si>
     <t>Variable name</t>
   </si>
@@ -4303,6 +4304,59 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A52E5EA-E759-42D2-80A5-71599DAF4092}">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA629D80-511C-42AD-ACB3-22237E3BD282}">
   <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
